--- a/tests/fixtures/danone/solicitud_servicios.xlsx
+++ b/tests/fixtures/danone/solicitud_servicios.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MODELO-A100</t>
+          <t>AVANT40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MODELO-A100</t>
+          <t>AT 200</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
